--- a/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_review.xlsx
+++ b/GearSage-client/pkgGear/data_raw/experiment_reports/review/2026-04-16_shimano_baitcasting_reel_whitelist_review.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:R31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,34 +418,46 @@
         <v>model</v>
       </c>
       <c r="E1" t="str">
+        <v>model_year</v>
+      </c>
+      <c r="F1" t="str">
         <v>sku</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>candidate_value</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>source_site</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>source_url</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>evidence_text</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>current_value_before_enrichment</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
+        <v>year_scope_note</v>
+      </c>
+      <c r="M1" t="str">
+        <v>fitment_note</v>
+      </c>
+      <c r="N1" t="str">
         <v>review_status</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>approved_value</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>reviewer</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>review_note</v>
+      </c>
+      <c r="R1" t="str">
+        <v>rejected_candidate_reason</v>
       </c>
     </row>
     <row r="2">
@@ -462,33 +474,45 @@
         <v>ANTARES DC</v>
       </c>
       <c r="E2" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F2" t="str">
         <v>ANTARES DC R</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="G2" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H2" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I2" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>Current whitelist source appears to describe the 2021 ANTARES DC. Do not reuse across other ANTARES DC years without year confirmation.</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -506,33 +530,45 @@
         <v>ANTARES DC</v>
       </c>
       <c r="E3" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F3" t="str">
         <v>ANTARES DC L</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="G3" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H3" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I3" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>Current whitelist source appears to describe the 2021 ANTARES DC. Do not reuse across other ANTARES DC years without year confirmation.</v>
       </c>
       <c r="M3" t="str">
         <v/>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
@@ -550,33 +586,45 @@
         <v>ANTARES DC</v>
       </c>
       <c r="E4" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F4" t="str">
         <v>ANTARES DC HG R</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="G4" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H4" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I4" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>Current whitelist source appears to describe the 2021 ANTARES DC. Do not reuse across other ANTARES DC years without year confirmation.</v>
       </c>
       <c r="M4" t="str">
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
@@ -594,33 +642,45 @@
         <v>ANTARES DC</v>
       </c>
       <c r="E5" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F5" t="str">
         <v>ANTARES DC HG L</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="G5" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H5" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I5" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>Current whitelist source appears to describe the 2021 ANTARES DC. Do not reuse across other ANTARES DC years without year confirmation.</v>
       </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
@@ -638,33 +698,45 @@
         <v>ANTARES DC</v>
       </c>
       <c r="E6" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F6" t="str">
         <v>ANTARES DC XG R</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="G6" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H6" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I6" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>Current whitelist source appears to describe the 2021 ANTARES DC. Do not reuse across other ANTARES DC years without year confirmation.</v>
       </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
@@ -682,33 +754,45 @@
         <v>ANTARES DC</v>
       </c>
       <c r="E7" t="str">
+        <v>2021</v>
+      </c>
+      <c r="F7" t="str">
         <v>ANTARES DC XG L</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="G7" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H7" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I7" t="str">
         <v>https://www.japantackle.com/casting-reels/shimano/shimano-21antaresdc.html</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>Hagane aluminum alloy body</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>Current whitelist source appears to describe the 2021 ANTARES DC. Do not reuse across other ANTARES DC years without year confirmation.</v>
       </c>
       <c r="M7" t="str">
         <v/>
       </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
@@ -726,33 +810,45 @@
         <v>ANTARES DC MD</v>
       </c>
       <c r="E8" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F8" t="str">
         <v>ANTARES DC MD HG RIGHT</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>metal frames</v>
       </c>
-      <c r="G8" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H8" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I8" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
       <c r="K8" t="str">
         <v/>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>2023 ANTARES DC MD needs year-bound review. Same-series material wording may differ by generation.</v>
       </c>
       <c r="M8" t="str">
         <v/>
       </c>
       <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
@@ -770,33 +866,45 @@
         <v>ANTARES DC MD</v>
       </c>
       <c r="E9" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F9" t="str">
         <v>ANTARES DC MD HG LEFT</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>metal frames</v>
       </c>
-      <c r="G9" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H9" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I9" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>2023 ANTARES DC MD needs year-bound review. Same-series material wording may differ by generation.</v>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
@@ -814,33 +922,45 @@
         <v>ANTARES DC MD</v>
       </c>
       <c r="E10" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F10" t="str">
         <v>ANTARES DC MD XG RIGHT</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>metal frames</v>
       </c>
-      <c r="G10" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H10" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I10" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>2023 ANTARES DC MD needs year-bound review. Same-series material wording may differ by generation.</v>
       </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
@@ -858,33 +978,45 @@
         <v>ANTARES DC MD</v>
       </c>
       <c r="E11" t="str">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="str">
         <v>ANTARES DC MD XG LEFT</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>metal frames</v>
       </c>
-      <c r="G11" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H11" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I11" t="str">
         <v>https://japantackle.com/casting-reels/shimano-23antares-dcmd.html</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>To maximize the chance to catch them, Antares DC MD has sturdy metal frames, enlarged 38mm dia, 21mm width spools, 20lb(JP)-100m line capacity, and fast gear ratios. MD tuned DC brake system is more finely tuned to draw the best performance from Magnum Light 3 spools to cast bulky large baits in comforts. Another ball bearing is added to main shaft support to remove plays and to improve cranking power.</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>2023 ANTARES DC MD needs year-bound review. Same-series material wording may differ by generation.</v>
       </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
@@ -902,33 +1034,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E12" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F12" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="G12" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H12" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I12" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
@@ -946,33 +1090,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E13" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F13" t="str">
         <v>Metanium DC 70</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="G13" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H13" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I13" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
@@ -990,33 +1146,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E14" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F14" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="G14" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H14" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I14" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M14" t="str">
         <v/>
       </c>
       <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
@@ -1034,33 +1202,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E15" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F15" t="str">
         <v>Metanium DC 71</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="G15" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H15" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I15" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
@@ -1078,33 +1258,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E16" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F16" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="G16" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H16" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I16" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
@@ -1122,33 +1314,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E17" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F17" t="str">
         <v>Metanium DC 70HG</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="G17" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H17" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I17" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
@@ -1166,33 +1370,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E18" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F18" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="G18" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H18" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I18" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
@@ -1210,33 +1426,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E19" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F19" t="str">
         <v>Metanium DC 71HG</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="G19" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H19" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I19" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
@@ -1254,33 +1482,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E20" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F20" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="G20" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H20" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I20" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
@@ -1298,33 +1538,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E21" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F21" t="str">
         <v>Metanium DC 70XG</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="G21" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H21" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I21" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
       <c r="K21" t="str">
         <v/>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
@@ -1342,33 +1594,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E22" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F22" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>Core solid metal body</v>
       </c>
-      <c r="G22" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H22" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I22" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>All New Shimano 2024 Metanium DC is the versatile bait caster for all around use. Core solid metal body holds every components solid. The state of arts i-DC5 brake system casts very smooth for long, and the new material dial is changeable without opening the side plate. MGL 3 spool offers fast spool acceleration.</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
       <c r="K22" t="str">
         <v/>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
         <v/>
       </c>
     </row>
@@ -1386,33 +1650,45 @@
         <v>Metanium DC</v>
       </c>
       <c r="E23" t="str">
+        <v>2024</v>
+      </c>
+      <c r="F23" t="str">
         <v>Metanium DC 71XG</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="G23" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H23" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I23" t="str">
         <v>https://japantackle.com/metaniumdc2024.html</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>Duralumin drive gear</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
       <c r="K23" t="str">
         <v/>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>Current source is treated as 2024 Metanium DC. Body/gear material may differ across other Metanium DC years.</v>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
         <v/>
       </c>
     </row>
@@ -1430,33 +1706,45 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
         <v>CALCUTTA CONQUEST BFS HG RIGHT</v>
       </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="G24" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H24" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I24" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
       <c r="K24" t="str">
         <v/>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>Calcutta Conquest BFS patch should keep reel_id and SKU binding. Do not spread by model-only match.</v>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
         <v/>
       </c>
     </row>
@@ -1474,33 +1762,45 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v>CALCUTTA CONQUEST BFS HG LEFT</v>
       </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="G25" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H25" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I25" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
       <c r="K25" t="str">
         <v/>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>Calcutta Conquest BFS patch should keep reel_id and SKU binding. Do not spread by model-only match.</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
         <v/>
       </c>
     </row>
@@ -1518,33 +1818,45 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
         <v>CALCUTTA CONQUEST BFS XG RIGHT</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="G26" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H26" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I26" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
       <c r="K26" t="str">
         <v/>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>Calcutta Conquest BFS patch should keep reel_id and SKU binding. Do not spread by model-only match.</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
         <v/>
       </c>
     </row>
@@ -1562,33 +1874,45 @@
         <v>CALCUTTA CONQUEST BFS</v>
       </c>
       <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>CALCUTTA CONQUEST BFS XG LEFT</v>
       </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="G27" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H27" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I27" t="str">
         <v>https://japantackle.com/casting-reels/shimano/reg0000334.html</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
         <v>Fully machined aluminum body and side plates</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
       <c r="K27" t="str">
         <v/>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>Calcutta Conquest BFS patch should keep reel_id and SKU binding. Do not spread by model-only match.</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
         <v/>
       </c>
     </row>
@@ -1606,33 +1930,45 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
         <v>ALDEBARAN BFS HG R</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="G28" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H28" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I28" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
       <c r="K28" t="str">
         <v/>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>Aldebaran BFS material claims must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
         <v/>
       </c>
     </row>
@@ -1650,33 +1986,45 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
         <v>ALDEBARAN BFS HG L</v>
       </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="G29" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H29" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I29" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
       <c r="K29" t="str">
         <v/>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>Aldebaran BFS material claims must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
         <v/>
       </c>
     </row>
@@ -1694,33 +2042,45 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
         <v>ALDEBARAN BFS XG R</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="G30" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H30" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I30" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
       <c r="K30" t="str">
         <v/>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>Aldebaran BFS material claims must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
         <v/>
       </c>
     </row>
@@ -1738,39 +2098,51 @@
         <v>ALDEBARAN BFS</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>ALDEBARAN BFS XG L</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="G31" t="str">
-        <v>JapanTackle</v>
-      </c>
       <c r="H31" t="str">
+        <v>JapanTackle</v>
+      </c>
+      <c r="I31" t="str">
         <v>https://japantackle.com/special/reg0000317.html</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <v>Hagane body system</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
       <c r="K31" t="str">
         <v/>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>Aldebaran BFS material claims must stay bound to reel_id and SKU until year/version is confirmed.</v>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R31"/>
   </ignoredErrors>
 </worksheet>
 </file>
